--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N105_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N105_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.57120192146231</v>
+        <v>9.680320312237626</v>
       </c>
       <c r="D2" t="n">
-        <v>59.85644811781007</v>
+        <v>9.726672819144138</v>
       </c>
       <c r="E2" t="n">
-        <v>6.229634814109688</v>
+        <v>1.012315657292824</v>
       </c>
       <c r="F2" t="n">
-        <v>6.218455008117707</v>
+        <v>1.010498938819127</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.27815384851491</v>
+        <v>8.982700000383673</v>
       </c>
       <c r="D3" t="n">
-        <v>66.7150312231411</v>
+        <v>10.84119257376043</v>
       </c>
       <c r="E3" t="n">
-        <v>6.229634814109688</v>
+        <v>1.012315657292824</v>
       </c>
       <c r="F3" t="n">
-        <v>6.218455008117707</v>
+        <v>1.010498938819127</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.59745406829643</v>
+        <v>10.49708628609817</v>
       </c>
       <c r="D4" t="n">
-        <v>64.32514886431179</v>
+        <v>10.45283669045067</v>
       </c>
       <c r="E4" t="n">
-        <v>6.229634814109688</v>
+        <v>1.012315657292824</v>
       </c>
       <c r="F4" t="n">
-        <v>6.218455008117707</v>
+        <v>1.010498938819127</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>72.55783753755328</v>
+        <v>11.79064859985241</v>
       </c>
       <c r="D5" t="n">
-        <v>72.82752733956168</v>
+        <v>11.83447319267877</v>
       </c>
       <c r="E5" t="n">
-        <v>6.229634814109688</v>
+        <v>1.012315657292824</v>
       </c>
       <c r="F5" t="n">
-        <v>6.218455008117707</v>
+        <v>1.010498938819127</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.40279981742108</v>
+        <v>8.352954970330925</v>
       </c>
       <c r="D6" t="n">
-        <v>51.12522812997952</v>
+        <v>8.307849571121672</v>
       </c>
       <c r="E6" t="n">
-        <v>6.229634814109688</v>
+        <v>1.012315657292824</v>
       </c>
       <c r="F6" t="n">
-        <v>6.218455008117707</v>
+        <v>1.010498938819127</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.16367992519477</v>
+        <v>9.289097987844151</v>
       </c>
       <c r="D7" t="n">
-        <v>57.23114611237988</v>
+        <v>9.300061243261732</v>
       </c>
       <c r="E7" t="n">
-        <v>6.229634814109688</v>
+        <v>1.012315657292824</v>
       </c>
       <c r="F7" t="n">
-        <v>6.218455008117707</v>
+        <v>1.010498938819127</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>57.51233958231161</v>
+        <v>9.345755182125638</v>
       </c>
       <c r="D8" t="n">
-        <v>57.35732796574133</v>
+        <v>9.320565794432968</v>
       </c>
       <c r="E8" t="n">
-        <v>6.229634814109688</v>
+        <v>1.012315657292824</v>
       </c>
       <c r="F8" t="n">
-        <v>6.218455008117707</v>
+        <v>1.010498938819127</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>61.24923066800406</v>
+        <v>9.95299998355066</v>
       </c>
       <c r="D9" t="n">
-        <v>61.05412380659568</v>
+        <v>9.921295118571798</v>
       </c>
       <c r="E9" t="n">
-        <v>6.229634814109688</v>
+        <v>1.012315657292824</v>
       </c>
       <c r="F9" t="n">
-        <v>6.218455008117707</v>
+        <v>1.010498938819127</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>68.01586840954447</v>
+        <v>11.05257861655098</v>
       </c>
       <c r="D10" t="n">
-        <v>67.92641367485241</v>
+        <v>11.03804222216352</v>
       </c>
       <c r="E10" t="n">
-        <v>6.229634814109688</v>
+        <v>1.012315657292824</v>
       </c>
       <c r="F10" t="n">
-        <v>6.218455008117707</v>
+        <v>1.010498938819127</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
